--- a/data/trans_bre/P36B08_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,78</t>
+          <t>0,78; 9,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,4</t>
+          <t>2,28; 11,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,36</t>
+          <t>-2,84; 6,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,94</t>
+          <t>-1,28; 3,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 14,07</t>
+          <t>1,04; 14,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 15,84</t>
+          <t>3,02; 15,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 8,87</t>
+          <t>-3,82; 8,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,22</t>
+          <t>-1,31; 3,43</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 11,04</t>
+          <t>1,9; 11,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,37</t>
+          <t>2,39; 10,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,72</t>
+          <t>0,89; 8,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,04</t>
+          <t>0,02; 3,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 18,61</t>
+          <t>3,02; 18,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 15,05</t>
+          <t>3,3; 15,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 12,49</t>
+          <t>1,22; 12,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,23</t>
+          <t>0,03; 3,92</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 17,77</t>
+          <t>7,77; 17,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,47</t>
+          <t>3,93; 13,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,02</t>
+          <t>1,27; 11,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 6,74</t>
+          <t>-1,88; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 32,66</t>
+          <t>12,78; 32,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 21,38</t>
+          <t>5,71; 22,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 17,28</t>
+          <t>1,8; 17,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 7,57</t>
+          <t>-1,97; 4,28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 11,55</t>
+          <t>3,23; 11,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 14,76</t>
+          <t>6,99; 14,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 10,04</t>
+          <t>3,03; 10,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,84</t>
+          <t>-0,2; 3,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 19,62</t>
+          <t>5,11; 20,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 21,1</t>
+          <t>9,2; 21,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 13,63</t>
+          <t>3,87; 13,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,29</t>
+          <t>-0,21; 4,29</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,3</t>
+          <t>5,65; 10,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,41</t>
+          <t>6,1; 10,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,07</t>
+          <t>2,83; 7,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,8</t>
+          <t>0,32; 2,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 16,75</t>
+          <t>8,72; 16,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,95</t>
+          <t>8,42; 14,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,94</t>
+          <t>3,86; 10,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,0</t>
+          <t>0,33; 2,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P36B08_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
